--- a/storage/bank-statements/Reopen_Test_HSBC_914031244.xlsx
+++ b/storage/bank-statements/Reopen_Test_HSBC_914031244.xlsx
@@ -469,12 +469,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20/03/2026</t>
+          <t>05/08/2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>PAYMENT INV 11172600006350 VOLTAIRE INC</t>
+          <t>T1 PAYMENT INV 11172600006350 VOLTAIRE INC</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -497,19 +497,19 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>REOPEN-R01</t>
+          <t>REOPEN-T1</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>20/03/2026</t>
+          <t>05/08/2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>REMIT 11172600003366 SITIME CORPORATION</t>
+          <t>T2 REMIT 11172600003366 SITIME CORPORATION</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -532,19 +532,19 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>REOPEN-R02</t>
+          <t>REOPEN-T2</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>20/03/2026</t>
+          <t>05/08/2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ACH 11172600006255 ASSURANT INC</t>
+          <t>T3 ACH 11172600006255 ASSURANT INC</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -567,19 +567,19 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>REOPEN-R03</t>
+          <t>REOPEN-T3</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>20/03/2026</t>
+          <t>05/08/2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>WIRE 11172600002745 UBER TECHNOLOGIES</t>
+          <t>T4 WIRE 11172600002745 UBER TECHNOLOGIES</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -602,19 +602,19 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>REOPEN-R04</t>
+          <t>REOPEN-T4</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>20/03/2026</t>
+          <t>05/08/2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>PAYMENT RECEIVED HACH COMPANY THANK YOU</t>
+          <t>T5 PAYMENT RECEIVED HACH COMPANY THANK YOU</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -637,19 +637,19 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>REOPEN-R05</t>
+          <t>REOPEN-T5</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>20/03/2026</t>
+          <t>05/08/2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>MISC CREDIT 88213 ADJUSTMENT NO REF</t>
+          <t>T6 MISC CREDIT 88213 ADJUSTMENT NO REF</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -672,19 +672,19 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>REOPEN-R06</t>
+          <t>REOPEN-T6</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>20/03/2026</t>
+          <t>05/08/2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>PMT 11172600003285 11172600003286 CEPHEID</t>
+          <t>T7 PMT 11172600003285 11172600003286 CEPHEID</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -707,19 +707,19 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>REOPEN-R07</t>
+          <t>REOPEN-T7</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>20/03/2026</t>
+          <t>05/08/2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>WIRE 11172600001566 MUUS COLLECTIVE</t>
+          <t>T8 WIRE 11172600001566 MUUS COLLECTIVE</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -742,19 +742,19 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>REOPEN-R08</t>
+          <t>REOPEN-T8</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>20/03/2026</t>
+          <t>05/08/2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ACH 11172600006119 BECKMAN COULTER INC</t>
+          <t>T9 ACH 11172600006119 BECKMAN COULTER INC</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -777,19 +777,19 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>REOPEN-R09</t>
+          <t>REOPEN-T9</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>20/03/2026</t>
+          <t>05/08/2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>REMIT 11172600005171 ESKO GRAPHICS BV</t>
+          <t>T10 REMIT 11172600005171 ESKO GRAPHICS BV</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -812,7 +812,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>REOPEN-R10</t>
+          <t>REOPEN-T10</t>
         </is>
       </c>
     </row>
@@ -855,12 +855,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>R01</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>REOPEN-R01</t>
+          <t>REOPEN-T1</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -868,19 +868,19 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>R9a exact match -&gt; Ready for Oracle</t>
+          <t>Ready for Oracle (R9a exact)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>R02</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>REOPEN-R02</t>
+          <t>REOPEN-T2</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -888,19 +888,19 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>R9b 5% short, no credit memos -&gt; Short Payment</t>
+          <t>Short Payment (R9b, 5% short, no credit memos)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>R03</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>REOPEN-R03</t>
+          <t>REOPEN-T3</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -908,19 +908,19 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>R9c short + customer holds credit memos -&gt; Conflict/Shortage</t>
+          <t>Conflict/Shortage (R9c - 7% short but customer holds credit memos)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>R04</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>REOPEN-R04</t>
+          <t>REOPEN-T4</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -928,19 +928,19 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>R11 large overpayment -&gt; Conflict (unexplained overpayment)</t>
+          <t>Conflict (R11 unexplained overpayment)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>R05</t>
+          <t>T5</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>REOPEN-R05</t>
+          <t>REOPEN-T5</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -948,19 +948,19 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>R7 customer only, no invoice -&gt; Needs Remittance</t>
+          <t>Unidentified with AI off (Needs Remittance with AI on)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>R06</t>
+          <t>T6</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>REOPEN-R06</t>
+          <t>REOPEN-T6</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -968,19 +968,19 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>R8 no signal -&gt; Unidentified</t>
+          <t>Unidentified (R8 no signal)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>R07</t>
+          <t>T7</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>REOPEN-R07</t>
+          <t>REOPEN-T7</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -988,19 +988,19 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>R9a multi-invoice exact -&gt; Ready for Oracle (2 invoices)</t>
+          <t>Ready for Oracle (R9a, two invoices)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>R08</t>
+          <t>T8</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>REOPEN-R08</t>
+          <t>REOPEN-T8</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -1008,19 +1008,19 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>R11 overpayment -&gt; park it, then reopen the PARKED row</t>
+          <t>Conflict (R11) - park it, then reopen the PARKED row</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>R09</t>
+          <t>T9</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>REOPEN-R09</t>
+          <t>REOPEN-T9</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -1028,19 +1028,19 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>R9a exact, customer has 9 invoices -&gt; remap to a sibling on reopen</t>
+          <t>Ready for Oracle (R9a) - remap to a sibling on reopen</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>R10</t>
+          <t>T10</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>REOPEN-R10</t>
+          <t>REOPEN-T10</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>R9a exact -&gt; reopen with NO edits (must land back unchanged)</t>
+          <t>Ready for Oracle (R9a) - the no-edit case</t>
         </is>
       </c>
     </row>
